--- a/uploads/empresas.xlsx
+++ b/uploads/empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gta\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27E2EB2-F783-4DC4-A819-EDA6C2A2453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CBA4AD-E5B6-4AC3-AC67-7E8EB6E497DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{02928549-E33A-417D-BBB0-DEE8D66D7C05}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="144">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -60,12 +60,6 @@
     <t>ACTIVO</t>
   </si>
   <si>
-    <t>EMPRESA DEMO</t>
-  </si>
-  <si>
-    <t>JUAN PEREZ</t>
-  </si>
-  <si>
     <t>PUEBLA</t>
   </si>
   <si>
@@ -78,22 +72,400 @@
     <t>601 - General de Ley Personas Morales</t>
   </si>
   <si>
-    <t>EMPRESA ABC</t>
-  </si>
-  <si>
-    <t>SONIA JUAREZ</t>
-  </si>
-  <si>
-    <t>ACTIVA</t>
-  </si>
-  <si>
-    <t>ABC1202284567</t>
-  </si>
-  <si>
-    <t>RFC1234123456</t>
-  </si>
-  <si>
-    <t>empresahotmail.com</t>
+    <t>ASESORIAS ESPECIALES DE MEXICO</t>
+  </si>
+  <si>
+    <t>AXIONES FINPRO</t>
+  </si>
+  <si>
+    <t>AGRICOLA FLAYTE</t>
+  </si>
+  <si>
+    <t>ASESORIAS INTEGRALES EL VOLCAN</t>
+  </si>
+  <si>
+    <t>ASESORIAS LOVEOLDI</t>
+  </si>
+  <si>
+    <t>AGRICOLA MARLIZ</t>
+  </si>
+  <si>
+    <t>ALIANZA DE NEGOCIOS ESTRATEGICOS ANG</t>
+  </si>
+  <si>
+    <t>SERVICIO LIVERA DE PROTECCION</t>
+  </si>
+  <si>
+    <t>ARGENTTO-EMPRESA DE PROTECCION EMPRESARIAL</t>
+  </si>
+  <si>
+    <t>BAIRES CONSULTORES</t>
+  </si>
+  <si>
+    <t>CONSTRUK EDIFICACIONES MODERNAS DEL CENTRO</t>
+  </si>
+  <si>
+    <t>CORPORATIVO INTERNACIONAL DE DISEÑO Y CONSTRUCCION LAS TORRES</t>
+  </si>
+  <si>
+    <t>BAMEX MEXICANA BAJOS</t>
+  </si>
+  <si>
+    <t>DCP CONSTRUCCIONES Y DESARROLLOS PUEBLA</t>
+  </si>
+  <si>
+    <t>DIOLVE CORPORACION</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA COMERCIAL DE PRODUCTOS MODERNOS</t>
+  </si>
+  <si>
+    <t>DESIGNIO EMPRESARIAL DELARVE</t>
+  </si>
+  <si>
+    <t>DIMAYER LEX</t>
+  </si>
+  <si>
+    <t>EMPRESA PARA EL COMERCIO AGRO-POBLANA</t>
+  </si>
+  <si>
+    <t>ESTILOS ITALIANO - VENECIA</t>
+  </si>
+  <si>
+    <t>FUNDACION ETERNIDAD</t>
+  </si>
+  <si>
+    <t>FTDM FUERZA TRABAJADORA DE MEXICO</t>
+  </si>
+  <si>
+    <t>PROYECTOS FME</t>
+  </si>
+  <si>
+    <t>FABRICANTES DE SOFTWARE Y SEGURIDAD SDM</t>
+  </si>
+  <si>
+    <t>GRUPO ASESOR PALMIRA</t>
+  </si>
+  <si>
+    <t>GRUPO BAREVILO</t>
+  </si>
+  <si>
+    <t>GRUPO CONSULTOR DE APOYO PROFESIONISTAS DEL SUR-APOY</t>
+  </si>
+  <si>
+    <t>GRUPO CONSTRUCTOR CCEM</t>
+  </si>
+  <si>
+    <t>GRUPO DE GASTRONOMIA Y ABASTECEDORA DE ALIMENTOS</t>
+  </si>
+  <si>
+    <t>GRUPO HSCR</t>
+  </si>
+  <si>
+    <t>GRUPO INMOBILIARIO HADOLMAN</t>
+  </si>
+  <si>
+    <t>GRUPOALRAVE</t>
+  </si>
+  <si>
+    <t>IDINEE</t>
+  </si>
+  <si>
+    <t>INGENIERIA EMPRESARIAL INEM</t>
+  </si>
+  <si>
+    <t>IDEATICO IMAGEN Y COMUNICACION</t>
+  </si>
+  <si>
+    <t>LOGISTICA DOLV-PACK</t>
+  </si>
+  <si>
+    <t>LOGISTICA ESTRATEGICA DE TRANSPORTACION SIN FRONTERAS NBK</t>
+  </si>
+  <si>
+    <t>LATINI LEGAL</t>
+  </si>
+  <si>
+    <t>MURRAY ANDINO DE SERVICIOS INMOBILIARIOS</t>
+  </si>
+  <si>
+    <t>LA MANCHA CONSULTORES</t>
+  </si>
+  <si>
+    <t>MIRIANOVA CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t>MULTISER DISTRIBUIDORA Y COMERCIALIZADORA</t>
+  </si>
+  <si>
+    <t>MARKETING EMPRESARIAL WH</t>
+  </si>
+  <si>
+    <t>MULTISOLUCIONES INTEGRALES EN NEGOCIOS EMPRESARIALES DE OCCIDENTE MINEM</t>
+  </si>
+  <si>
+    <t>NUBITECH SYSTEMS</t>
+  </si>
+  <si>
+    <t>OPERADORA TURISTICA ALTAMAR</t>
+  </si>
+  <si>
+    <t>PROFESIONISTAS ASOCIADOS WORLDWORKING</t>
+  </si>
+  <si>
+    <t>PRECISION TECNICA INDUSTRIAL Y BALANCEO DINAMICO</t>
+  </si>
+  <si>
+    <t>RH-MADECO</t>
+  </si>
+  <si>
+    <t>RECLUTAMIENTO Y SELECCION DE PERSONAL SIGLO XXI</t>
+  </si>
+  <si>
+    <t>RYZEN SYSTEMS</t>
+  </si>
+  <si>
+    <t>SAGUSO-NEG</t>
+  </si>
+  <si>
+    <t>SERVICIOS BOCHIARG</t>
+  </si>
+  <si>
+    <t>SUPERNOVA EDECANES</t>
+  </si>
+  <si>
+    <t>SECTOR FINPLAT</t>
+  </si>
+  <si>
+    <t>SOLUCIONES INTEGRALES DE LIMPIEZA Y MANTENIMIENTO BIO CLEAN</t>
+  </si>
+  <si>
+    <t>SINDICATO INDUSTRIAL DE TRABAJADORES OBREROS Y EMPLEADOS ADMVOS DE EMPRESAS DE TRANSPORTE DE SERVICIOS ADMINISTRATIVOS CONTABLES DE VIGILANCIA COMERCIAL DE PUBLICIDAD DE MERCADOTECNIA INMOBILIARIA TRANSPORTE TURISMO Y ASISTENCIA SOCIAL SIMILARES ANEXOS Y</t>
+  </si>
+  <si>
+    <t>SERVICIOS DE LIMPIEZA Y MANTENIMIENTO ASTRETT</t>
+  </si>
+  <si>
+    <t>SERVICIO MEDICO ESPECIALIZADO DEL SUR MEDISUR</t>
+  </si>
+  <si>
+    <t>SECTOR ODAGOBA</t>
+  </si>
+  <si>
+    <t>SINDICATO DE TRABAJADORES DE BIENES Y SERVICIOS Y DE LA PRODUCCION BLAS CHUMACERO SANCHEZ DEL ESTADO DE PUEBLA</t>
+  </si>
+  <si>
+    <t>UNION DE PEPENADORES Y RECOLECTORES DE DESPERDICIOS DE LA REPUBLICA MEXICANA</t>
+  </si>
+  <si>
+    <t>YUVISTRONG</t>
+  </si>
+  <si>
+    <t>OPERACIONES ESTRUCTURADAS NORTE SUR</t>
+  </si>
+  <si>
+    <t>AEM090703C66</t>
+  </si>
+  <si>
+    <t>AFI2411215W7</t>
+  </si>
+  <si>
+    <t>AFL230124GE7</t>
+  </si>
+  <si>
+    <t>AIV191001HZ8</t>
+  </si>
+  <si>
+    <t>ALO2209191M7</t>
+  </si>
+  <si>
+    <t>AMA120502SY3</t>
+  </si>
+  <si>
+    <t>ANE220329E69</t>
+  </si>
+  <si>
+    <t>APE101119KX3</t>
+  </si>
+  <si>
+    <t>APE231124HN5</t>
+  </si>
+  <si>
+    <t>BCO240821BG5</t>
+  </si>
+  <si>
+    <t>CEM210813115</t>
+  </si>
+  <si>
+    <t>CID101011BD8</t>
+  </si>
+  <si>
+    <t>CPC121112P65</t>
+  </si>
+  <si>
+    <t>DCD210813Q90</t>
+  </si>
+  <si>
+    <t>DCO230614QY7</t>
+  </si>
+  <si>
+    <t>DCP1202108T0</t>
+  </si>
+  <si>
+    <t>DED230908VE4</t>
+  </si>
+  <si>
+    <t>DLE2502252U1</t>
+  </si>
+  <si>
+    <t>ECA120928RL5</t>
+  </si>
+  <si>
+    <t>EIG1608114S8</t>
+  </si>
+  <si>
+    <t>FET0711307V3</t>
+  </si>
+  <si>
+    <t>FFT2104095EA</t>
+  </si>
+  <si>
+    <t>FMP220902PR4</t>
+  </si>
+  <si>
+    <t>FSS200904J71</t>
+  </si>
+  <si>
+    <t>GAP240301Q46</t>
+  </si>
+  <si>
+    <t>GBA2201122H3</t>
+  </si>
+  <si>
+    <t>GCA171129463</t>
+  </si>
+  <si>
+    <t>GCC220210EB5</t>
+  </si>
+  <si>
+    <t>GGA131211FS9</t>
+  </si>
+  <si>
+    <t>GHS190919BH4</t>
+  </si>
+  <si>
+    <t>GIH2211308G7</t>
+  </si>
+  <si>
+    <t>GRU110622E47</t>
+  </si>
+  <si>
+    <t>IDI2201203Q0</t>
+  </si>
+  <si>
+    <t>IEI1001222Z2</t>
+  </si>
+  <si>
+    <t>IIC120705LJ7</t>
+  </si>
+  <si>
+    <t>LDO221221SE1</t>
+  </si>
+  <si>
+    <t>LET210906EB9</t>
+  </si>
+  <si>
+    <t>LLE240816G16</t>
+  </si>
+  <si>
+    <t>MAS120214R35</t>
+  </si>
+  <si>
+    <t>MCO0804152M8</t>
+  </si>
+  <si>
+    <t>MCO231108S32</t>
+  </si>
+  <si>
+    <t>MDC2204061Q8</t>
+  </si>
+  <si>
+    <t>MEW2009048A3</t>
+  </si>
+  <si>
+    <t>MIN130422TF7</t>
+  </si>
+  <si>
+    <t>NSY241218R79</t>
+  </si>
+  <si>
+    <t>OTA160308G84</t>
+  </si>
+  <si>
+    <t>PAW180320GM4</t>
+  </si>
+  <si>
+    <t>PTI0509083K7</t>
+  </si>
+  <si>
+    <t>RHM2307279Z7</t>
+  </si>
+  <si>
+    <t>RSP200130PF8</t>
+  </si>
+  <si>
+    <t>RSY2212218X5</t>
+  </si>
+  <si>
+    <t>SAG230927GJ1</t>
+  </si>
+  <si>
+    <t>SBO2301097JA</t>
+  </si>
+  <si>
+    <t>SEM120705RH0</t>
+  </si>
+  <si>
+    <t>SFI221124CD0</t>
+  </si>
+  <si>
+    <t>SIL220131ME7</t>
+  </si>
+  <si>
+    <t>SIT100202SE3</t>
+  </si>
+  <si>
+    <t>SLM1203056B3</t>
+  </si>
+  <si>
+    <t>SME180116HS2</t>
+  </si>
+  <si>
+    <t>SOD230817TL7</t>
+  </si>
+  <si>
+    <t>STB1611156B4</t>
+  </si>
+  <si>
+    <t>UPR110125SF6</t>
+  </si>
+  <si>
+    <t>YUV191003Q49</t>
+  </si>
+  <si>
+    <t>OEN071129H35</t>
+  </si>
+  <si>
+    <t>626 - Régimen Simplificado de Confianza</t>
+  </si>
+  <si>
+    <t>603 - Personas Morales con Fines no Lucrativos</t>
+  </si>
+  <si>
+    <t>620 - Sociedades Cooperativas de Producción que optan por diferir sus ingresos</t>
+  </si>
+  <si>
+    <t>LIC. HERNAN PEREZ PEREZ</t>
   </si>
 </sst>
 </file>
@@ -462,8 +834,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CF9E7D-61D2-463C-A6EC-245E31654DB0}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="95.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -488,62 +865,1486 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2">
-        <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="2">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="2">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="2">
         <v>13</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="2">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18">
         <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="2">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>141</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="2">
+        <v>21</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24">
+        <v>22</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="2">
+        <v>23</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>24</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="2">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="2">
+        <v>27</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30">
+        <v>28</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>140</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="2">
+        <v>29</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32">
+        <v>30</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="2">
+        <v>31</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34">
+        <v>32</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="2">
+        <v>33</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36">
+        <v>34</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>140</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="2">
+        <v>35</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38">
+        <v>36</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="2">
+        <v>37</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>140</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40">
+        <v>38</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="2">
+        <v>39</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42">
+        <v>40</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="2">
+        <v>41</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="2">
+        <v>43</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46">
+        <v>44</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48">
+        <v>46</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+      <c r="H48" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="2">
+        <v>47</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50">
+        <v>48</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="2">
+        <v>49</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>140</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52">
+        <v>50</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="2">
+        <v>51</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54">
+        <v>52</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="2">
+        <v>53</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56">
+        <v>54</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="2">
+        <v>55</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58">
+        <v>56</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>141</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="2">
+        <v>57</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60">
+        <v>58</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="2">
+        <v>59</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62">
+        <v>60</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>141</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="2">
+        <v>61</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64">
+        <v>62</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>140</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="2">
+        <v>63</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
